--- a/artfynd/A 34519-2022 artfynd.xlsx
+++ b/artfynd/A 34519-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34519-2022 artfynd.xlsx
+++ b/artfynd/A 34519-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104778203</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956362</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -974,6 +989,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958946</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1071,6 +1091,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960475</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1168,6 +1193,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958298</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1265,6 +1295,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969089</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1373,6 +1408,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104778328</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1470,6 +1510,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966127</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1567,6 +1612,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134955725</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1675,6 +1725,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104778682</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104779239</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1891,6 +1951,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104778301</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1999,6 +2064,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104780368</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2096,6 +2166,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134955509</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2193,6 +2268,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956491</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2290,6 +2370,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958945</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2387,6 +2472,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960481</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2484,6 +2574,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965499</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2581,6 +2676,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966128</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2678,6 +2778,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969464</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2775,6 +2880,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134971118</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2883,6 +2993,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104780537</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2991,6 +3106,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104778294</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3088,6 +3208,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965500</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3206,6 +3331,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95295543</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3328,6 +3458,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95296324</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3429,6 +3564,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956489</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3530,6 +3670,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958729</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3631,6 +3776,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959537</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3732,6 +3882,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966765</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3833,6 +3988,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970270</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3934,6 +4094,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134971119</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4042,6 +4207,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104778332</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4139,6 +4309,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959747</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4247,6 +4422,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104779986</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4344,6 +4524,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959139</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4441,6 +4626,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966559</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4538,6 +4728,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134957888</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4635,6 +4830,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960686</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4732,6 +4932,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965498</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4829,6 +5034,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966345</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4931,6 +5141,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134971336</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5033,6 +5248,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966349</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5134,8 +5354,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959140</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 34519-2022 artfynd.xlsx
+++ b/artfynd/A 34519-2022 artfynd.xlsx
@@ -796,7 +796,7 @@
         <v>134956362</v>
       </c>
       <c r="B3" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>134958946</v>
       </c>
       <c r="B4" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>134960475</v>
       </c>
       <c r="B5" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>134958298</v>
       </c>
       <c r="B6" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>134969089</v>
       </c>
       <c r="B7" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>134966127</v>
       </c>
       <c r="B9" t="n">
-        <v>92188</v>
+        <v>92230</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>134955725</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>134955509</v>
       </c>
       <c r="B15" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>134956491</v>
       </c>
       <c r="B16" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>134958945</v>
       </c>
       <c r="B17" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>134960481</v>
       </c>
       <c r="B18" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>134965499</v>
       </c>
       <c r="B19" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>134966128</v>
       </c>
       <c r="B20" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>134969464</v>
       </c>
       <c r="B21" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>134971118</v>
       </c>
       <c r="B22" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>134965500</v>
       </c>
       <c r="B25" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>134956489</v>
       </c>
       <c r="B28" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>134958729</v>
       </c>
       <c r="B29" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>134959537</v>
       </c>
       <c r="B30" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>134966765</v>
       </c>
       <c r="B31" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>134970270</v>
       </c>
       <c r="B32" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>134971119</v>
       </c>
       <c r="B33" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>134959747</v>
       </c>
       <c r="B35" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>134959139</v>
       </c>
       <c r="B37" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>134966559</v>
       </c>
       <c r="B38" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>134957888</v>
       </c>
       <c r="B39" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>134960686</v>
       </c>
       <c r="B40" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>134965498</v>
       </c>
       <c r="B41" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>134966345</v>
       </c>
       <c r="B42" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>134971336</v>
       </c>
       <c r="B43" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>134966349</v>
       </c>
       <c r="B44" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>134959140</v>
       </c>
       <c r="B45" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
